--- a/setup/categorisation/Keelan-Decisions.xlsx
+++ b/setup/categorisation/Keelan-Decisions.xlsx
@@ -11,12 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tena and Durex moves" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tag removals not done" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock these or drop the page" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Azio title typo" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Medium confidence'!$A$3:$I$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tena and Durex moves'!$A$3:$I$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tag removals not done'!$A$3:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stock these or drop the page'!$A$3:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Azio title typo'!$A$3:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4886,4 +4888,121 @@
   <autoFilter ref="A3:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="96" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>1 product title misspelled — hold until after launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Found by the homepage offers session on 1 Oct 2026 and left alone by both of us. Not a categorisation problem, and deliberately not fixed during the sweep: it is a URL change dressed up as a typo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Product title now</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Handle now</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Why it is not a one-field edit</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>After launch</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Azio Beuty Refining Micro Exfoliator</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>azio-beuty-refining-micro-exfoliator</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Azio Beauty</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>fix title + handle + redirect + regenerate, in one change</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>The misspelling is in the handle as well as the title, so it is a URL change and not a one-field edit. Correcting the handle breaks /products/azio-beuty-refining-micro-exfoliator, and setup/redirects.csv already points the old-site URL at that misspelled handle, so the redirect target moves too. redirects.csv is generated by build_redirects.py, so editing it by hand gets overwritten on the next run. The vendor is spelled correctly ("Azio Beauty"), so no brand page is affected and nothing is broken today.</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>